--- a/outputs/match_sensors_output.xlsx
+++ b/outputs/match_sensors_output.xlsx
@@ -1,43 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Outros computadores\O meu portátil\DOUTORADO\UMRAE\PAPER2\smarthphone_sound_calibration\outputs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A43F8ED-EFA6-4F29-8C89-B73598F26B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="28">
   <si>
     <t>device</t>
   </si>
   <si>
+    <t>p1</t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>p1-sensor</t>
+  </si>
+  <si>
+    <t>p2-sensor</t>
+  </si>
+  <si>
     <t>E1-Aluno1</t>
   </si>
   <si>
@@ -53,31 +46,55 @@
     <t>E1-Aluno5</t>
   </si>
   <si>
-    <t>p1-sensor</t>
+    <t>E2-Aluno1</t>
+  </si>
+  <si>
+    <t>E2-Aluno2</t>
+  </si>
+  <si>
+    <t>E2-Aluno3</t>
+  </si>
+  <si>
+    <t>E2-Aluno4</t>
+  </si>
+  <si>
+    <t>E2-Aluno5</t>
+  </si>
+  <si>
+    <t>14:48:46</t>
+  </si>
+  <si>
+    <t>14:48:47</t>
+  </si>
+  <si>
+    <t>16:20:03</t>
+  </si>
+  <si>
+    <t>15:06:32</t>
+  </si>
+  <si>
+    <t>15:06:30</t>
+  </si>
+  <si>
+    <t>15:06:29</t>
+  </si>
+  <si>
+    <t>15:21:00</t>
+  </si>
+  <si>
+    <t>15:20:59</t>
+  </si>
+  <si>
+    <t>15:21:02</t>
+  </si>
+  <si>
+    <t>15:20:58</t>
   </si>
   <si>
     <t>fixsensor-m2</t>
   </si>
   <si>
-    <t>E2-Aluno1</t>
-  </si>
-  <si>
     <t>fixsensor-m4</t>
-  </si>
-  <si>
-    <t>E2-Aluno2</t>
-  </si>
-  <si>
-    <t>E2-Aluno3</t>
-  </si>
-  <si>
-    <t>E2-Aluno4</t>
-  </si>
-  <si>
-    <t>E2-Aluno5</t>
-  </si>
-  <si>
-    <t>p2-sensor</t>
   </si>
   <si>
     <t>referenceiphone-m10</t>
@@ -86,8 +103,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,21 +167,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -202,7 +211,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -236,7 +245,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -271,10 +279,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -447,116 +454,162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="18.44140625" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>13</v>
-      </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/match_sensors_output.xlsx
+++ b/outputs/match_sensors_output.xlsx
@@ -91,13 +91,13 @@
     <t>15:20:58</t>
   </si>
   <si>
-    <t>fixsensor-m2</t>
-  </si>
-  <si>
-    <t>fixsensor-m4</t>
-  </si>
-  <si>
-    <t>referenceiphone-m10</t>
+    <t>sensorA-m2</t>
+  </si>
+  <si>
+    <t>sensorA-m4</t>
+  </si>
+  <si>
+    <t>sensorB-m10</t>
   </si>
 </sst>
 </file>
